--- a/result/train_info_group_part_detrend_plr_stft_bin_win_fi.xlsx
+++ b/result/train_info_group_part_detrend_plr_stft_bin_win_fi.xlsx
@@ -17,16 +17,13 @@
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
 <styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <numFmts count="0"/>
-  <fonts count="2">
+  <fonts count="1">
     <font>
       <name val="Calibri"/>
       <family val="2"/>
       <color theme="1"/>
       <sz val="11"/>
       <scheme val="minor"/>
-    </font>
-    <font>
-      <b val="1"/>
     </font>
   </fonts>
   <fills count="2">
@@ -37,7 +34,7 @@
       <patternFill patternType="gray125"/>
     </fill>
   </fills>
-  <borders count="2">
+  <borders count="1">
     <border>
       <left/>
       <right/>
@@ -45,21 +42,12 @@
       <bottom/>
       <diagonal/>
     </border>
-    <border>
-      <left style="thin"/>
-      <right style="thin"/>
-      <top style="thin"/>
-      <bottom style="thin"/>
-    </border>
   </borders>
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="2">
+  <cellXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
-    <xf numFmtId="0" fontId="1" fillId="0" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
-      <alignment horizontal="center" vertical="top"/>
-    </xf>
   </cellXfs>
   <cellStyles count="1">
     <cellStyle name="Normal" xfId="0" builtinId="0" hidden="0"/>
@@ -429,32 +417,32 @@
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
-      <c r="A1" s="1" t="inlineStr">
+      <c r="A1" t="inlineStr">
         <is>
           <t>model</t>
         </is>
       </c>
-      <c r="B1" s="1" t="inlineStr">
+      <c r="B1" t="inlineStr">
         <is>
           <t>time</t>
         </is>
       </c>
-      <c r="C1" s="1" t="inlineStr">
+      <c r="C1" t="inlineStr">
         <is>
           <t>precision</t>
         </is>
       </c>
-      <c r="D1" s="1" t="inlineStr">
+      <c r="D1" t="inlineStr">
         <is>
           <t>recall</t>
         </is>
       </c>
-      <c r="E1" s="1" t="inlineStr">
+      <c r="E1" t="inlineStr">
         <is>
           <t>f1</t>
         </is>
       </c>
-      <c r="F1" s="1" t="inlineStr">
+      <c r="F1" t="inlineStr">
         <is>
           <t>test_acc</t>
         </is>
@@ -467,19 +455,19 @@
         </is>
       </c>
       <c r="B2" t="n">
-        <v>2.605993986129761</v>
+        <v>1.717233896255493</v>
       </c>
       <c r="C2" t="n">
-        <v>0.9315068493150684</v>
+        <v>0.9408682634730539</v>
       </c>
       <c r="D2" t="n">
-        <v>0.9325426241660489</v>
+        <v>0.9318013343217197</v>
       </c>
       <c r="E2" t="n">
-        <v>0.9320244489720318</v>
+        <v>0.9363128491620112</v>
       </c>
       <c r="F2" t="n">
-        <v>0.9318097361575622</v>
+        <v>0.9364548494983278</v>
       </c>
     </row>
     <row r="3">
@@ -489,19 +477,19 @@
         </is>
       </c>
       <c r="B3" t="n">
-        <v>20.2057785987854</v>
+        <v>13.19837403297424</v>
       </c>
       <c r="C3" t="n">
-        <v>0.9892353377876764</v>
+        <v>0.9899553571428571</v>
       </c>
       <c r="D3" t="n">
-        <v>0.9877687175685693</v>
+        <v>0.986286137879911</v>
       </c>
       <c r="E3" t="n">
-        <v>0.9885014836795252</v>
+        <v>0.9881173412551059</v>
       </c>
       <c r="F3" t="n">
-        <v>0.9884801189149015</v>
+        <v>0.9881085098476403</v>
       </c>
     </row>
     <row r="4">
@@ -511,19 +499,19 @@
         </is>
       </c>
       <c r="B4" t="n">
-        <v>0.00812220573425293</v>
+        <v>0.006999015808105469</v>
       </c>
       <c r="C4" t="n">
-        <v>0.9966567607726597</v>
+        <v>0.9962908011869436</v>
       </c>
       <c r="D4" t="n">
-        <v>0.9944403261675315</v>
+        <v>0.9955522609340252</v>
       </c>
       <c r="E4" t="n">
-        <v>0.9955473098330241</v>
+        <v>0.9959213941416388</v>
       </c>
       <c r="F4" t="n">
-        <v>0.9955406911928651</v>
+        <v>0.9959123002601263</v>
       </c>
     </row>
     <row r="5">
@@ -533,19 +521,19 @@
         </is>
       </c>
       <c r="B5" t="n">
-        <v>0.1410806179046631</v>
+        <v>0.4605915546417236</v>
       </c>
       <c r="C5" t="n">
-        <v>0.7760747663551402</v>
+        <v>0.7836190476190477</v>
       </c>
       <c r="D5" t="n">
-        <v>0.7694588584136397</v>
+        <v>0.762416604892513</v>
       </c>
       <c r="E5" t="n">
-        <v>0.7727526521496371</v>
+        <v>0.7728724403531843</v>
       </c>
       <c r="F5" t="n">
-        <v>0.7731326644370122</v>
+        <v>0.7753623188405797</v>
       </c>
     </row>
     <row r="6">
@@ -555,19 +543,19 @@
         </is>
       </c>
       <c r="B6" t="n">
-        <v>4.215638160705566</v>
+        <v>57.23473906517029</v>
       </c>
       <c r="C6" t="n">
-        <v>0.931059772643931</v>
+        <v>0.9357090374724467</v>
       </c>
       <c r="D6" t="n">
-        <v>0.941067457375834</v>
+        <v>0.9440326167531505</v>
       </c>
       <c r="E6" t="n">
-        <v>0.9360368663594471</v>
+        <v>0.9398523985239853</v>
       </c>
       <c r="F6" t="n">
-        <v>0.9355258268301747</v>
+        <v>0.9394277220364177</v>
       </c>
     </row>
   </sheetData>
